--- a/pay2.xlsx
+++ b/pay2.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="253">
   <si>
     <t>#</t>
   </si>
@@ -170,64 +170,61 @@
     <t>جاسم محمد عبد الله عبد</t>
   </si>
   <si>
+    <t>جعفر نضال كاظم احمد</t>
+  </si>
+  <si>
+    <t>1,350,000</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>جنيد زياد هادي حمد</t>
+  </si>
+  <si>
+    <t>حسن حيدر كاظم فلحي</t>
+  </si>
+  <si>
+    <t>2,060,000</t>
+  </si>
+  <si>
+    <t>190,000</t>
+  </si>
+  <si>
+    <t>91.56%</t>
+  </si>
+  <si>
+    <t>مسدد 75%+</t>
+  </si>
+  <si>
+    <t>حسن سعدون مزهر شنيور</t>
+  </si>
+  <si>
+    <t>560,000</t>
+  </si>
+  <si>
+    <t>1,690,000</t>
+  </si>
+  <si>
+    <t>24.89%</t>
+  </si>
+  <si>
+    <t>حسن طالب حسين صادق</t>
+  </si>
+  <si>
+    <t>1,250,000</t>
+  </si>
+  <si>
+    <t>1,000,000</t>
+  </si>
+  <si>
+    <t>حسين فراس عكار مطير</t>
+  </si>
+  <si>
+    <t>1,800,000</t>
+  </si>
+  <si>
     <t>1,150,000</t>
-  </si>
-  <si>
-    <t>48.89%</t>
-  </si>
-  <si>
-    <t>جعفر نضال كاظم احمد</t>
-  </si>
-  <si>
-    <t>1,350,000</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>جنيد زياد هادي حمد</t>
-  </si>
-  <si>
-    <t>حسن حيدر كاظم فلحي</t>
-  </si>
-  <si>
-    <t>2,060,000</t>
-  </si>
-  <si>
-    <t>190,000</t>
-  </si>
-  <si>
-    <t>91.56%</t>
-  </si>
-  <si>
-    <t>مسدد 75%+</t>
-  </si>
-  <si>
-    <t>حسن سعدون مزهر شنيور</t>
-  </si>
-  <si>
-    <t>560,000</t>
-  </si>
-  <si>
-    <t>1,690,000</t>
-  </si>
-  <si>
-    <t>24.89%</t>
-  </si>
-  <si>
-    <t>حسن طالب حسين صادق</t>
-  </si>
-  <si>
-    <t>1,250,000</t>
-  </si>
-  <si>
-    <t>1,000,000</t>
-  </si>
-  <si>
-    <t>حسين فراس عكار مطير</t>
-  </si>
-  <si>
-    <t>1,800,000</t>
   </si>
   <si>
     <t>650,000</t>
@@ -1644,32 +1641,32 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>27</v>
+      <c r="C16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1677,7 +1674,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>10</v>
@@ -1692,10 +1689,10 @@
         <v>40</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>27</v>
@@ -1706,7 +1703,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
@@ -1735,28 +1732,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1764,25 +1761,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>47</v>
@@ -1793,22 +1790,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>41</v>
@@ -1822,25 +1819,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>16</v>
@@ -1851,7 +1848,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>10</v>
@@ -1863,10 +1860,10 @@
         <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>41</v>
@@ -1880,7 +1877,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>10</v>
@@ -1895,10 +1892,10 @@
         <v>40</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>27</v>
@@ -1909,28 +1906,28 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="I25" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1938,7 +1935,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>10</v>
@@ -1956,7 +1953,7 @@
         <v>13</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>27</v>
@@ -1967,7 +1964,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>10</v>
@@ -1996,28 +1993,28 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="I28" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2025,7 +2022,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
@@ -2054,7 +2051,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
@@ -2083,7 +2080,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -2112,7 +2109,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>10</v>
@@ -2141,19 +2138,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" s="3">
         <v>0</v>
@@ -2170,28 +2167,28 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="I34" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2199,7 +2196,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
@@ -2228,7 +2225,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>10</v>
@@ -2257,28 +2254,28 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="6" t="s">
+      <c r="G37" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>100</v>
-      </c>
       <c r="I37" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2286,7 +2283,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>10</v>
@@ -2298,16 +2295,16 @@
         <v>39</v>
       </c>
       <c r="F38" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="I38" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2315,7 +2312,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>10</v>
@@ -2344,7 +2341,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>10</v>
@@ -2373,7 +2370,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>10</v>
@@ -2402,7 +2399,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>10</v>
@@ -2414,16 +2411,16 @@
         <v>12</v>
       </c>
       <c r="F42" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="I42" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2431,7 +2428,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>10</v>
@@ -2460,7 +2457,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>10</v>
@@ -2489,7 +2486,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>10</v>
@@ -2518,25 +2515,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>16</v>
@@ -2547,7 +2544,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
@@ -2559,13 +2556,13 @@
         <v>38</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G47" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>16</v>
@@ -2576,25 +2573,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>16</v>
@@ -2605,7 +2602,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>10</v>
@@ -2634,25 +2631,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="H50" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>16</v>
@@ -2663,28 +2660,28 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="6" t="s">
+      <c r="G51" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="H51" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H51" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="I51" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2692,28 +2689,28 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="6" t="s">
+      <c r="G52" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H52" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="I52" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2721,7 +2718,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>10</v>
@@ -2750,25 +2747,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="5" t="s">
+      <c r="G54" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="H54" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>47</v>
@@ -2779,7 +2776,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
@@ -2794,10 +2791,10 @@
         <v>30</v>
       </c>
       <c r="G55" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>16</v>
@@ -2808,7 +2805,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
@@ -2823,10 +2820,10 @@
         <v>25</v>
       </c>
       <c r="G56" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>16</v>
@@ -2837,7 +2834,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>10</v>
@@ -2866,7 +2863,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>10</v>
@@ -2895,28 +2892,28 @@
         <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F59" s="6" t="s">
+      <c r="G59" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>151</v>
-      </c>
       <c r="H59" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2924,7 +2921,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>10</v>
@@ -2953,7 +2950,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>10</v>
@@ -2982,7 +2979,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>10</v>
@@ -3011,7 +3008,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -3040,7 +3037,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>10</v>
@@ -3052,16 +3049,16 @@
         <v>12</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H64" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="I64" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3069,25 +3066,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="H65" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>47</v>
@@ -3098,7 +3095,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>10</v>
@@ -3127,7 +3124,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>10</v>
@@ -3156,25 +3153,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H68" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>47</v>
@@ -3185,7 +3182,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>10</v>
@@ -3214,25 +3211,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G70" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>16</v>
@@ -3243,7 +3240,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>10</v>
@@ -3272,7 +3269,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>10</v>
@@ -3284,16 +3281,16 @@
         <v>12</v>
       </c>
       <c r="F72" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="H72" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H72" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="I72" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3301,25 +3298,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="4" t="s">
+      <c r="G73" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>27</v>
@@ -3330,7 +3327,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>10</v>
@@ -3359,7 +3356,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>10</v>
@@ -3388,7 +3385,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>10</v>
@@ -3400,13 +3397,13 @@
         <v>12</v>
       </c>
       <c r="F76" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="H76" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>16</v>
@@ -3417,7 +3414,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>10</v>
@@ -3429,16 +3426,16 @@
         <v>12</v>
       </c>
       <c r="F77" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G77" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G77" s="6" t="s">
+      <c r="H77" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H77" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="I77" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3446,7 +3443,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>10</v>
@@ -3475,28 +3472,28 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H79" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="I79" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3504,7 +3501,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>10</v>
@@ -3533,7 +3530,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>10</v>
@@ -3562,7 +3559,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>10</v>
@@ -3574,13 +3571,13 @@
         <v>12</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>47</v>
@@ -3591,7 +3588,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>10</v>
@@ -3603,13 +3600,13 @@
         <v>12</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>16</v>
@@ -3620,7 +3617,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>10</v>
@@ -3649,7 +3646,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>10</v>
@@ -3678,7 +3675,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>10</v>
@@ -3690,16 +3687,16 @@
         <v>12</v>
       </c>
       <c r="F86" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G86" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G86" s="6" t="s">
+      <c r="H86" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H86" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="I86" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3707,7 +3704,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>10</v>
@@ -3719,13 +3716,13 @@
         <v>39</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G87" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>27</v>
@@ -3736,25 +3733,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F88" s="4" t="s">
+      <c r="G88" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>27</v>
@@ -3765,7 +3762,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>10</v>
@@ -3794,7 +3791,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>10</v>
@@ -3823,25 +3820,25 @@
         <v>90</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H91" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="I91" s="5" t="s">
         <v>47</v>
@@ -3852,7 +3849,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>10</v>
@@ -3864,16 +3861,16 @@
         <v>12</v>
       </c>
       <c r="F92" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G92" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G92" s="6" t="s">
+      <c r="H92" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H92" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="I92" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3881,7 +3878,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>10</v>
@@ -3910,7 +3907,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>10</v>
@@ -3939,7 +3936,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3965,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>10</v>
@@ -3997,28 +3994,28 @@
         <v>96</v>
       </c>
       <c r="B97" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97" s="6" t="s">
+      <c r="G97" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G97" s="6" t="s">
+      <c r="H97" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="H97" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="I97" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4026,7 +4023,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>10</v>
@@ -4055,7 +4052,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>10</v>
@@ -4067,13 +4064,13 @@
         <v>38</v>
       </c>
       <c r="F99" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="H99" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>16</v>
@@ -4084,25 +4081,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H100" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>27</v>
@@ -4113,7 +4110,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>10</v>
@@ -4142,7 +4139,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>10</v>
@@ -4171,28 +4168,28 @@
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" s="6" t="s">
+      <c r="G103" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G103" s="6" t="s">
+      <c r="H103" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="H103" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="I103" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -4200,7 +4197,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>10</v>
@@ -4209,10 +4206,10 @@
         <v>11</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G104" s="3">
         <v>0</v>
@@ -4229,7 +4226,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>10</v>
@@ -4258,7 +4255,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>10</v>
@@ -4287,25 +4284,25 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H107" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="I107" s="5" t="s">
         <v>47</v>
@@ -4316,7 +4313,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>10</v>
@@ -4325,10 +4322,10 @@
         <v>11</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G108" s="3">
         <v>0</v>
@@ -4345,7 +4342,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>10</v>
@@ -4360,10 +4357,10 @@
         <v>25</v>
       </c>
       <c r="G109" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>16</v>
@@ -4374,7 +4371,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>10</v>
@@ -4403,7 +4400,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>10</v>
@@ -4415,10 +4412,10 @@
         <v>12</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>41</v>
@@ -4432,25 +4429,25 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C112" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="5" t="s">
+      <c r="G112" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="H112" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>47</v>
@@ -4461,7 +4458,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>10</v>
@@ -4473,13 +4470,13 @@
         <v>12</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I113" s="5" t="s">
         <v>47</v>
@@ -4490,7 +4487,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>10</v>
@@ -4519,7 +4516,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>10</v>
@@ -4531,10 +4528,10 @@
         <v>12</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>41</v>
@@ -4548,7 +4545,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>10</v>
@@ -4560,13 +4557,13 @@
         <v>12</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I116" s="5" t="s">
         <v>47</v>
@@ -4577,7 +4574,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>10</v>
@@ -4589,13 +4586,13 @@
         <v>12</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>27</v>
@@ -4606,7 +4603,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>10</v>
@@ -4618,16 +4615,16 @@
         <v>39</v>
       </c>
       <c r="F118" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G118" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="G118" s="6" t="s">
-        <v>244</v>
-      </c>
       <c r="H118" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4635,7 +4632,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>10</v>
@@ -4664,25 +4661,25 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120" s="2" t="s">
+      <c r="G120" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="H120" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>16</v>
@@ -4693,7 +4690,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>10</v>
@@ -4722,25 +4719,25 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G122" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G122" s="2" t="s">
+      <c r="H122" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>16</v>

--- a/pay2.xlsx
+++ b/pay2.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="245">
   <si>
     <t>#</t>
   </si>
@@ -263,228 +263,222 @@
     <t>حيدر غسان جليل اسماعيل</t>
   </si>
   <si>
+    <t>دعاء علي حسين علي</t>
+  </si>
+  <si>
+    <t>دلال سعدي ناجي داود</t>
+  </si>
+  <si>
+    <t>رحاب نهاد خزعل ابراهيم</t>
+  </si>
+  <si>
+    <t>رقيه حسين عدنان مهدي</t>
+  </si>
+  <si>
+    <t>ريام عز الدين جلوب حمادي</t>
+  </si>
+  <si>
+    <t>562,500</t>
+  </si>
+  <si>
+    <t>ريم حاتم جابر دحيح</t>
+  </si>
+  <si>
+    <t>1,700,000</t>
+  </si>
+  <si>
+    <t>550,000</t>
+  </si>
+  <si>
+    <t>75.56%</t>
+  </si>
+  <si>
+    <t>ريم يونس مزيغر منصور</t>
+  </si>
+  <si>
+    <t>زهراء عبد الخضر كاظم عبيد</t>
+  </si>
+  <si>
+    <t>زهراء فراس جاسم حمادي</t>
+  </si>
+  <si>
+    <t>1,825,000</t>
+  </si>
+  <si>
+    <t>425,000</t>
+  </si>
+  <si>
+    <t>81.11%</t>
+  </si>
+  <si>
+    <t>زيد احمد سالم حسن</t>
+  </si>
+  <si>
+    <t>1,110,000</t>
+  </si>
+  <si>
+    <t>15,000</t>
+  </si>
+  <si>
+    <t>98.67%</t>
+  </si>
+  <si>
+    <t>زينب حسن انور مصطفى</t>
+  </si>
+  <si>
+    <t>سارة احمد جواد كاظم</t>
+  </si>
+  <si>
+    <t>سما صفاء بشان عبيد</t>
+  </si>
+  <si>
+    <t>سما صلاح حسن حسين</t>
+  </si>
+  <si>
+    <t>شهد صالح حميد جواد</t>
+  </si>
+  <si>
+    <t>صادق طاهر جاسم محمد</t>
+  </si>
+  <si>
+    <t>صفا حسين حمود محمد</t>
+  </si>
+  <si>
+    <t>ضحى راضي علي سلوم</t>
+  </si>
+  <si>
+    <t>1,300,000</t>
+  </si>
+  <si>
+    <t>950,000</t>
+  </si>
+  <si>
+    <t>57.78%</t>
+  </si>
+  <si>
+    <t>طارق صلاح ياسر موسى</t>
+  </si>
+  <si>
+    <t>775,000</t>
+  </si>
+  <si>
+    <t>61.73%</t>
+  </si>
+  <si>
+    <t>طيبه ايهاب نافع عيد</t>
+  </si>
+  <si>
+    <t>1,625,000</t>
+  </si>
+  <si>
+    <t>625,000</t>
+  </si>
+  <si>
+    <t>72.22%</t>
+  </si>
+  <si>
+    <t>عباس رائد علي محمد</t>
+  </si>
+  <si>
+    <t>عباس علي حسين علي</t>
+  </si>
+  <si>
+    <t>1,660,000</t>
+  </si>
+  <si>
+    <t>590,000</t>
+  </si>
+  <si>
+    <t>73.78%</t>
+  </si>
+  <si>
+    <t>عبد الجليل خالد عبد الجليل ثعبان</t>
+  </si>
+  <si>
+    <t>1,695,000</t>
+  </si>
+  <si>
+    <t>555,000</t>
+  </si>
+  <si>
+    <t>75.33%</t>
+  </si>
+  <si>
+    <t>عبد الرحمن عباس محمود علي</t>
+  </si>
+  <si>
+    <t>1,950,000</t>
+  </si>
+  <si>
+    <t>300,000</t>
+  </si>
+  <si>
+    <t>86.67%</t>
+  </si>
+  <si>
+    <t>عبد الله محمود اسماعيل جواد</t>
+  </si>
+  <si>
+    <t>عبد الله معمر موفق حمود</t>
+  </si>
+  <si>
+    <t>400,000</t>
+  </si>
+  <si>
+    <t>1,850,000</t>
+  </si>
+  <si>
+    <t>17.78%</t>
+  </si>
+  <si>
+    <t>عبد الوهاب ثامر محمد حسن</t>
+  </si>
+  <si>
+    <t>925,000</t>
+  </si>
+  <si>
+    <t>54.32%</t>
+  </si>
+  <si>
+    <t>علي سليمان عبد حسون</t>
+  </si>
+  <si>
+    <t>علي عادل نعمه</t>
+  </si>
+  <si>
+    <t>علي فرحان جاسم محمد</t>
+  </si>
+  <si>
+    <t>علي فلاح حسن فاضل</t>
+  </si>
+  <si>
+    <t>1,560,000</t>
+  </si>
+  <si>
+    <t>240,000</t>
+  </si>
+  <si>
+    <t>عمار صباح عبد الستار احمد</t>
+  </si>
+  <si>
+    <t>ليلى سالم عبد اللطيف عبد الكريم</t>
+  </si>
+  <si>
+    <t>ماّب عامر عبد القادر فليح</t>
+  </si>
+  <si>
+    <t>محمد باقر نجم متعب</t>
+  </si>
+  <si>
+    <t>محمد جاسم محمد حسون</t>
+  </si>
+  <si>
     <t>450,000</t>
   </si>
   <si>
     <t>80%</t>
   </si>
   <si>
-    <t>دعاء علي حسين علي</t>
-  </si>
-  <si>
-    <t>دلال سعدي ناجي داود</t>
-  </si>
-  <si>
-    <t>رحاب نهاد خزعل ابراهيم</t>
-  </si>
-  <si>
-    <t>رقيه حسين عدنان مهدي</t>
-  </si>
-  <si>
-    <t>ريام عز الدين جلوب حمادي</t>
-  </si>
-  <si>
-    <t>562,500</t>
-  </si>
-  <si>
-    <t>ريم حاتم جابر دحيح</t>
-  </si>
-  <si>
-    <t>1,700,000</t>
-  </si>
-  <si>
-    <t>550,000</t>
-  </si>
-  <si>
-    <t>75.56%</t>
-  </si>
-  <si>
-    <t>ريم يونس مزيغر منصور</t>
-  </si>
-  <si>
-    <t>زهراء عبد الخضر كاظم عبيد</t>
-  </si>
-  <si>
-    <t>زهراء فراس جاسم حمادي</t>
-  </si>
-  <si>
-    <t>1,825,000</t>
-  </si>
-  <si>
-    <t>425,000</t>
-  </si>
-  <si>
-    <t>81.11%</t>
-  </si>
-  <si>
-    <t>زيد احمد سالم حسن</t>
-  </si>
-  <si>
-    <t>1,110,000</t>
-  </si>
-  <si>
-    <t>15,000</t>
-  </si>
-  <si>
-    <t>98.67%</t>
-  </si>
-  <si>
-    <t>زينب حسن انور مصطفى</t>
-  </si>
-  <si>
-    <t>سارة احمد جواد كاظم</t>
-  </si>
-  <si>
-    <t>سما صفاء بشان عبيد</t>
-  </si>
-  <si>
-    <t>سما صلاح حسن حسين</t>
-  </si>
-  <si>
-    <t>شهد صالح حميد جواد</t>
-  </si>
-  <si>
-    <t>صادق طاهر جاسم محمد</t>
-  </si>
-  <si>
-    <t>صفا حسين حمود محمد</t>
-  </si>
-  <si>
-    <t>ضحى راضي علي سلوم</t>
-  </si>
-  <si>
-    <t>1,300,000</t>
-  </si>
-  <si>
-    <t>950,000</t>
-  </si>
-  <si>
-    <t>57.78%</t>
-  </si>
-  <si>
-    <t>طارق صلاح ياسر موسى</t>
-  </si>
-  <si>
-    <t>775,000</t>
-  </si>
-  <si>
-    <t>61.73%</t>
-  </si>
-  <si>
-    <t>طيبه ايهاب نافع عيد</t>
-  </si>
-  <si>
-    <t>1,625,000</t>
-  </si>
-  <si>
-    <t>625,000</t>
-  </si>
-  <si>
-    <t>72.22%</t>
-  </si>
-  <si>
-    <t>عباس رائد علي محمد</t>
-  </si>
-  <si>
-    <t>عباس علي حسين علي</t>
-  </si>
-  <si>
-    <t>1,660,000</t>
-  </si>
-  <si>
-    <t>590,000</t>
-  </si>
-  <si>
-    <t>73.78%</t>
-  </si>
-  <si>
-    <t>عبد الجليل خالد عبد الجليل ثعبان</t>
-  </si>
-  <si>
-    <t>1,695,000</t>
-  </si>
-  <si>
-    <t>555,000</t>
-  </si>
-  <si>
-    <t>75.33%</t>
-  </si>
-  <si>
-    <t>عبد الرحمن عباس محمود علي</t>
-  </si>
-  <si>
-    <t>1,950,000</t>
-  </si>
-  <si>
-    <t>300,000</t>
-  </si>
-  <si>
-    <t>86.67%</t>
-  </si>
-  <si>
-    <t>عبد الله محمود اسماعيل جواد</t>
-  </si>
-  <si>
-    <t>عبد الله معمر موفق حمود</t>
-  </si>
-  <si>
-    <t>400,000</t>
-  </si>
-  <si>
-    <t>1,850,000</t>
-  </si>
-  <si>
-    <t>17.78%</t>
-  </si>
-  <si>
-    <t>عبد الوهاب ثامر محمد حسن</t>
-  </si>
-  <si>
-    <t>925,000</t>
-  </si>
-  <si>
-    <t>54.32%</t>
-  </si>
-  <si>
-    <t>علي سليمان عبد حسون</t>
-  </si>
-  <si>
-    <t>525,000</t>
-  </si>
-  <si>
-    <t>74.07%</t>
-  </si>
-  <si>
-    <t>علي عادل نعمه</t>
-  </si>
-  <si>
-    <t>علي فرحان جاسم محمد</t>
-  </si>
-  <si>
-    <t>علي فلاح حسن فاضل</t>
-  </si>
-  <si>
-    <t>1,560,000</t>
-  </si>
-  <si>
-    <t>240,000</t>
-  </si>
-  <si>
-    <t>عمار صباح عبد الستار احمد</t>
-  </si>
-  <si>
-    <t>ليلى سالم عبد اللطيف عبد الكريم</t>
-  </si>
-  <si>
-    <t>ماّب عامر عبد القادر فليح</t>
-  </si>
-  <si>
-    <t>محمد باقر نجم متعب</t>
-  </si>
-  <si>
-    <t>محمد جاسم محمد حسون</t>
-  </si>
-  <si>
     <t>محمد جمال كاظم احمد</t>
   </si>
   <si>
@@ -638,15 +632,6 @@
     <t>بهاء الدين احمد عويد كيطان</t>
   </si>
   <si>
-    <t>1,980,000</t>
-  </si>
-  <si>
-    <t>270,000</t>
-  </si>
-  <si>
-    <t>88%</t>
-  </si>
-  <si>
     <t>حيدر علي حسين كاظم</t>
   </si>
   <si>
@@ -714,15 +699,6 @@
   </si>
   <si>
     <t>مصطفى خلف عبد الله وهيب</t>
-  </si>
-  <si>
-    <t>250,000</t>
-  </si>
-  <si>
-    <t>2,000,000</t>
-  </si>
-  <si>
-    <t>11.11%</t>
   </si>
   <si>
     <t>مصطفى محمود صالح</t>
@@ -1989,32 +1965,32 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>59</v>
+      <c r="C28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2022,7 +1998,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
@@ -2051,7 +2027,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
@@ -2080,7 +2056,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -2109,7 +2085,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>10</v>
@@ -2138,7 +2114,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
@@ -2147,10 +2123,10 @@
         <v>11</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G33" s="3">
         <v>0</v>
@@ -2167,25 +2143,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>59</v>
@@ -2196,7 +2172,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
@@ -2225,7 +2201,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>10</v>
@@ -2254,25 +2230,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>59</v>
@@ -2283,7 +2259,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>10</v>
@@ -2295,13 +2271,13 @@
         <v>39</v>
       </c>
       <c r="F38" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>59</v>
@@ -2312,7 +2288,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>10</v>
@@ -2341,7 +2317,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>10</v>
@@ -2370,7 +2346,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>10</v>
@@ -2395,32 +2371,32 @@
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="6">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>59</v>
+      <c r="B42" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2428,7 +2404,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>10</v>
@@ -2457,7 +2433,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>10</v>
@@ -2486,7 +2462,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>10</v>
@@ -2515,25 +2491,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>16</v>
@@ -2544,7 +2520,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
@@ -2559,10 +2535,10 @@
         <v>65</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>16</v>
@@ -2573,25 +2549,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>16</v>
@@ -2602,7 +2578,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>10</v>
@@ -2631,25 +2607,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="H50" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>16</v>
@@ -2660,25 +2636,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="6" t="s">
+      <c r="H51" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>59</v>
@@ -2689,25 +2665,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>59</v>
@@ -2718,7 +2694,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>10</v>
@@ -2747,25 +2723,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="5" t="s">
+      <c r="H54" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>47</v>
@@ -2776,7 +2752,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
@@ -2791,42 +2767,42 @@
         <v>30</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="B56" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>16</v>
+      <c r="F56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2834,7 +2810,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>10</v>
@@ -2863,7 +2839,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>10</v>
@@ -2892,7 +2868,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>10</v>
@@ -2904,13 +2880,13 @@
         <v>68</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>59</v>
@@ -2921,7 +2897,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>10</v>
@@ -2950,7 +2926,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>10</v>
@@ -2979,7 +2955,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>10</v>
@@ -3008,7 +2984,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -3037,7 +3013,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>10</v>
@@ -3052,10 +3028,10 @@
         <v>68</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>59</v>
@@ -3066,25 +3042,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G65" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="5" t="s">
+      <c r="H65" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>47</v>
@@ -3095,7 +3071,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>10</v>
@@ -3124,7 +3100,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>10</v>
@@ -3153,7 +3129,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>10</v>
@@ -3171,7 +3147,7 @@
         <v>75</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>47</v>
@@ -3182,7 +3158,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>10</v>
@@ -3211,7 +3187,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>10</v>
@@ -3220,16 +3196,16 @@
         <v>11</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>16</v>
@@ -3240,7 +3216,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>10</v>
@@ -3269,7 +3245,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>10</v>
@@ -3281,13 +3257,13 @@
         <v>12</v>
       </c>
       <c r="F72" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>59</v>
@@ -3298,25 +3274,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>27</v>
@@ -3327,7 +3303,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>10</v>
@@ -3356,7 +3332,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>10</v>
@@ -3381,32 +3357,32 @@
       </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>16</v>
+      <c r="B76" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3414,7 +3390,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>10</v>
@@ -3426,13 +3402,13 @@
         <v>12</v>
       </c>
       <c r="F77" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H77" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>59</v>
@@ -3443,7 +3419,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>10</v>
@@ -3472,7 +3448,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>10</v>
@@ -3484,13 +3460,13 @@
         <v>12</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>59</v>
@@ -3501,7 +3477,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>10</v>
@@ -3530,7 +3506,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>10</v>
@@ -3559,7 +3535,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>10</v>
@@ -3577,7 +3553,7 @@
         <v>75</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>47</v>
@@ -3588,7 +3564,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>10</v>
@@ -3606,7 +3582,7 @@
         <v>40</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>16</v>
@@ -3617,7 +3593,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>10</v>
@@ -3646,7 +3622,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>10</v>
@@ -3675,7 +3651,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>10</v>
@@ -3704,7 +3680,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>10</v>
@@ -3719,10 +3695,10 @@
         <v>61</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>27</v>
@@ -3733,25 +3709,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>27</v>
@@ -3762,7 +3738,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>10</v>
@@ -3791,7 +3767,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>10</v>
@@ -3820,7 +3796,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>10</v>
@@ -3832,13 +3808,13 @@
         <v>12</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I91" s="5" t="s">
         <v>47</v>
@@ -3849,7 +3825,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>10</v>
@@ -3861,13 +3837,13 @@
         <v>12</v>
       </c>
       <c r="F92" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I92" s="6" t="s">
         <v>59</v>
@@ -3878,7 +3854,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>10</v>
@@ -3907,7 +3883,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>10</v>
@@ -3936,7 +3912,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>10</v>
@@ -3965,7 +3941,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>10</v>
@@ -3990,32 +3966,32 @@
       </c>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" s="6">
+      <c r="A97" s="3">
         <v>96</v>
       </c>
-      <c r="B97" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>59</v>
+      <c r="B97" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" s="3">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4023,7 +3999,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>10</v>
@@ -4052,7 +4028,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>10</v>
@@ -4064,13 +4040,13 @@
         <v>38</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>16</v>
@@ -4081,7 +4057,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>10</v>
@@ -4099,7 +4075,7 @@
         <v>65</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>27</v>
@@ -4110,7 +4086,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>10</v>
@@ -4139,7 +4115,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>10</v>
@@ -4168,7 +4144,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>10</v>
@@ -4180,13 +4156,13 @@
         <v>12</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I103" s="6" t="s">
         <v>59</v>
@@ -4197,7 +4173,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>10</v>
@@ -4206,10 +4182,10 @@
         <v>11</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G104" s="3">
         <v>0</v>
@@ -4226,7 +4202,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>10</v>
@@ -4255,7 +4231,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>10</v>
@@ -4284,7 +4260,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>10</v>
@@ -4296,13 +4272,13 @@
         <v>12</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I107" s="5" t="s">
         <v>47</v>
@@ -4313,7 +4289,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>10</v>
@@ -4338,32 +4314,32 @@
       </c>
     </row>
     <row r="109" spans="1:9">
-      <c r="A109" s="2">
+      <c r="A109" s="3">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="2" t="s">
+      <c r="B109" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>16</v>
+      <c r="F109" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G109" s="3">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4371,7 +4347,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>10</v>
@@ -4400,7 +4376,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>10</v>
@@ -4425,32 +4401,32 @@
       </c>
     </row>
     <row r="112" spans="1:9">
-      <c r="A112" s="5">
+      <c r="A112" s="3">
         <v>111</v>
       </c>
-      <c r="B112" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>47</v>
+      <c r="B112" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G112" s="3">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4458,7 +4434,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>10</v>
@@ -4476,7 +4452,7 @@
         <v>75</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I113" s="5" t="s">
         <v>47</v>
@@ -4487,7 +4463,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>10</v>
@@ -4512,32 +4488,32 @@
       </c>
     </row>
     <row r="115" spans="1:9">
-      <c r="A115" s="2">
+      <c r="A115" s="3">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>16</v>
+      <c r="B115" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="3">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4545,7 +4521,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>10</v>
@@ -4563,7 +4539,7 @@
         <v>75</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I116" s="5" t="s">
         <v>47</v>
@@ -4574,7 +4550,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>10</v>
@@ -4592,7 +4568,7 @@
         <v>65</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>27</v>
@@ -4603,7 +4579,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>10</v>
@@ -4615,13 +4591,13 @@
         <v>39</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I118" s="6" t="s">
         <v>59</v>
@@ -4632,7 +4608,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>10</v>
@@ -4661,7 +4637,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>10</v>
@@ -4673,13 +4649,13 @@
         <v>12</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>16</v>
@@ -4690,7 +4666,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>10</v>
@@ -4719,7 +4695,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>10</v>
@@ -4728,16 +4704,16 @@
         <v>11</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>16</v>

--- a/pay2.xlsx
+++ b/pay2.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="248">
   <si>
     <t>#</t>
   </si>
@@ -714,6 +714,15 @@
   </si>
   <si>
     <t>ندى علي عبد الحسين ابراهيم</t>
+  </si>
+  <si>
+    <t>2,000,000</t>
+  </si>
+  <si>
+    <t>250,000</t>
+  </si>
+  <si>
+    <t>88.89%</t>
   </si>
   <si>
     <t>نور صباح صالح نصرالله</t>
@@ -4546,32 +4555,32 @@
       </c>
     </row>
     <row r="117" spans="1:9">
-      <c r="A117" s="4">
+      <c r="A117" s="6">
         <v>116</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="I117" s="4" t="s">
-        <v>27</v>
+      <c r="C117" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4579,7 +4588,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>10</v>
@@ -4591,10 +4600,10 @@
         <v>39</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>132</v>
@@ -4608,7 +4617,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>10</v>
@@ -4637,7 +4646,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>10</v>
@@ -4649,13 +4658,13 @@
         <v>12</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>16</v>
@@ -4666,7 +4675,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>10</v>
@@ -4695,7 +4704,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>10</v>
@@ -4710,10 +4719,10 @@
         <v>66</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>16</v>
